--- a/TRANSPORTS/SHREE GANPATI LOGISTIC AND TRANSPORT.xlsx
+++ b/TRANSPORTS/SHREE GANPATI LOGISTIC AND TRANSPORT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapil\Desktop\RITIK KHANDELWAL\TRANSPORTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TRANSPORTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392F27E5-6CD7-46D3-B0B9-E15F1AF86015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7E2BBC-2E69-41AC-869E-7027441D077A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="2" activeTab="3" xr2:uid="{318E46D1-7443-436B-A252-67B114A40C51}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{318E46D1-7443-436B-A252-67B114A40C51}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMMARY" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="110">
   <si>
     <t>SEEMA SAREE CENTRE</t>
   </si>
@@ -2423,11 +2423,11 @@
       </c>
       <c r="B7" s="8">
         <f>SUM('JULY 2026'!$H$1:$H$1000)</f>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C7" s="9">
         <f>COUNTIF('JULY 2026'!$G$1:$G$1000, "L")</f>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D7" s="10">
         <f>COUNTIF('JULY 2026'!$G$1:$G$1000, "B")</f>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="F7" s="11">
         <f t="shared" ref="F7:F15" si="1">$C7*$H$2</f>
-        <v>21600</v>
+        <v>26400</v>
       </c>
       <c r="G7" s="12">
         <f t="shared" ref="G7:G15" si="2">$D7*$H$3</f>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="H7" s="13">
         <f t="shared" ref="H7:H15" si="3">SUM($F7,$G7)</f>
-        <v>22650</v>
+        <v>27450</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -2721,11 +2721,11 @@
       </c>
       <c r="B17" s="15">
         <f t="shared" ref="B17:H17" si="4">SUM(B6:B15)</f>
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C17" s="15">
         <f t="shared" si="4"/>
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D17" s="15">
         <f t="shared" si="4"/>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="F17" s="15">
         <f t="shared" si="4"/>
-        <v>174400</v>
+        <v>179200</v>
       </c>
       <c r="G17" s="15">
         <f t="shared" si="4"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H17" s="16">
         <f t="shared" si="4"/>
-        <v>177550</v>
+        <v>182350</v>
       </c>
     </row>
   </sheetData>
@@ -8088,7 +8088,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{232F15C0-67A4-4B1B-B6B8-2ABC4AAF2C02}">
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
@@ -8734,7 +8734,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D33">
         <v>187064</v>
       </c>
@@ -8754,7 +8754,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D34">
         <v>187638</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D35">
         <v>187077</v>
       </c>
@@ -8794,7 +8794,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D36">
         <v>187641</v>
       </c>
@@ -8814,6 +8814,138 @@
         <v>109</v>
       </c>
       <c r="J36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>46212</v>
+      </c>
+      <c r="B38">
+        <v>2914</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38">
+        <v>188138</v>
+      </c>
+      <c r="E38">
+        <v>10305</v>
+      </c>
+      <c r="F38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" t="s">
+        <v>71</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="J38" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D39">
+        <v>187952</v>
+      </c>
+      <c r="E39">
+        <v>530</v>
+      </c>
+      <c r="F39" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" t="s">
+        <v>71</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="J39" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D40">
+        <v>188139</v>
+      </c>
+      <c r="E40">
+        <v>10332</v>
+      </c>
+      <c r="F40" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" t="s">
+        <v>71</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="J40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D41">
+        <v>188038</v>
+      </c>
+      <c r="E41">
+        <v>10248</v>
+      </c>
+      <c r="F41" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" t="s">
+        <v>71</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="J41" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D42">
+        <v>187957</v>
+      </c>
+      <c r="E42">
+        <v>529</v>
+      </c>
+      <c r="F42" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" t="s">
+        <v>71</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="J42" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D43">
+        <v>187950</v>
+      </c>
+      <c r="E43">
+        <v>531</v>
+      </c>
+      <c r="F43" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" t="s">
+        <v>71</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>33</v>
+      </c>
+      <c r="J43" t="s">
         <v>61</v>
       </c>
     </row>
